--- a/SGC-CKN/Excel/32547bab-dab3-4c98-8bce-d4cbb9226443_Cọc_khoan_nhồi_P1-57_D800_02-04-2026.xlsx
+++ b/SGC-CKN/Excel/32547bab-dab3-4c98-8bce-d4cbb9226443_Cọc_khoan_nhồi_P1-57_D800_02-04-2026.xlsx
@@ -1142,7 +1142,7 @@
         <v>28</v>
       </c>
       <c r="F11" s="5">
-        <v>-0.84</v>
+        <v>0</v>
       </c>
       <c r="G11" s="5">
         <v>-1.4</v>
@@ -1151,10 +1151,10 @@
         <v>0.42</v>
       </c>
       <c r="I11" s="5">
-        <v>0.56</v>
+        <v>1.4</v>
       </c>
       <c r="J11" s="8">
-        <v>1.34</v>
+        <v>3.36</v>
       </c>
       <c r="K11" s="6" t="s">
         <v>29</v>
@@ -1554,7 +1554,7 @@
         <v>1</v>
       </c>
       <c r="E2" s="5">
-        <v>-0.84</v>
+        <v>0</v>
       </c>
       <c r="F2" s="5">
         <v>-1.4</v>
@@ -1563,10 +1563,10 @@
         <v>0.42</v>
       </c>
       <c r="H2" s="5">
-        <v>0.56</v>
+        <v>1.4</v>
       </c>
       <c r="I2" s="8">
-        <v>1.34</v>
+        <v>3.36</v>
       </c>
     </row>
     <row r="3" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1786,7 +1786,7 @@
         <v>8</v>
       </c>
       <c r="E10" s="33">
-        <v>-0.84</v>
+        <v>0</v>
       </c>
       <c r="F10" s="33">
         <v>-44.44</v>
@@ -1795,10 +1795,10 @@
         <v>7.25</v>
       </c>
       <c r="H10" s="33">
-        <v>43.6</v>
+        <v>44.44</v>
       </c>
       <c r="I10" s="33">
-        <v>6.01</v>
+        <v>6.13</v>
       </c>
     </row>
   </sheetData>
